--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124263147</v>
+        <v>124262395</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östrahult, Östrahult, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580916</v>
+        <v>580974</v>
       </c>
       <c r="R2" t="n">
-        <v>6380395</v>
+        <v>6380423</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124263681</v>
+        <v>124263147</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Östrahult, Östrahult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581062</v>
+        <v>580916</v>
       </c>
       <c r="R3" t="n">
-        <v>6380241</v>
+        <v>6380395</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124262395</v>
+        <v>124263681</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580974</v>
+        <v>581062</v>
       </c>
       <c r="R4" t="n">
-        <v>6380423</v>
+        <v>6380241</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124262395</v>
+        <v>124263681</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580974</v>
+        <v>581062</v>
       </c>
       <c r="R2" t="n">
-        <v>6380423</v>
+        <v>6380241</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124263681</v>
+        <v>124262395</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581062</v>
+        <v>580974</v>
       </c>
       <c r="R4" t="n">
-        <v>6380241</v>
+        <v>6380423</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124262395</v>
+        <v>124261792</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580974</v>
+        <v>581053</v>
       </c>
       <c r="R4" t="n">
-        <v>6380423</v>
+        <v>6380261</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124261792</v>
+        <v>124262395</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581053</v>
+        <v>580974</v>
       </c>
       <c r="R5" t="n">
-        <v>6380261</v>
+        <v>6380423</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124263681</v>
+        <v>124263147</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Östrahult, Östrahult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581062</v>
+        <v>580916</v>
       </c>
       <c r="R2" t="n">
-        <v>6380241</v>
+        <v>6380395</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124263147</v>
+        <v>124261792</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östrahult, Östrahult, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580916</v>
+        <v>581053</v>
       </c>
       <c r="R3" t="n">
-        <v>6380395</v>
+        <v>6380261</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124261792</v>
+        <v>124263681</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +911,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581053</v>
+        <v>581062</v>
       </c>
       <c r="R4" t="n">
-        <v>6380261</v>
+        <v>6380241</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124263147</v>
+        <v>124261792</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östrahult, Östrahult, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580916</v>
+        <v>581053</v>
       </c>
       <c r="R2" t="n">
-        <v>6380395</v>
+        <v>6380261</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124261792</v>
+        <v>124263147</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Östrahult, Östrahult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581053</v>
+        <v>580916</v>
       </c>
       <c r="R3" t="n">
-        <v>6380261</v>
+        <v>6380395</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124263681</v>
+        <v>124262395</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581062</v>
+        <v>580974</v>
       </c>
       <c r="R4" t="n">
-        <v>6380241</v>
+        <v>6380423</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124262395</v>
+        <v>124263681</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580974</v>
+        <v>581062</v>
       </c>
       <c r="R5" t="n">
-        <v>6380423</v>
+        <v>6380241</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124261792</v>
+        <v>124262395</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581053</v>
+        <v>580974</v>
       </c>
       <c r="R2" t="n">
-        <v>6380261</v>
+        <v>6380423</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124263147</v>
+        <v>124261792</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östrahult, Östrahult, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580916</v>
+        <v>581053</v>
       </c>
       <c r="R3" t="n">
-        <v>6380395</v>
+        <v>6380261</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124262395</v>
+        <v>124263681</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580974</v>
+        <v>581062</v>
       </c>
       <c r="R4" t="n">
-        <v>6380423</v>
+        <v>6380241</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124263681</v>
+        <v>124263147</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,46 +1028,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Östrahult, Östrahult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581062</v>
+        <v>580916</v>
       </c>
       <c r="R5" t="n">
-        <v>6380241</v>
+        <v>6380395</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124262395</v>
+        <v>124261792</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580974</v>
+        <v>581053</v>
       </c>
       <c r="R2" t="n">
-        <v>6380423</v>
+        <v>6380261</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124261792</v>
+        <v>124262395</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581053</v>
+        <v>580974</v>
       </c>
       <c r="R3" t="n">
-        <v>6380261</v>
+        <v>6380423</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124261792</v>
+        <v>124262395</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581053</v>
+        <v>580974</v>
       </c>
       <c r="R2" t="n">
-        <v>6380261</v>
+        <v>6380423</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124262395</v>
+        <v>124261792</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580974</v>
+        <v>581053</v>
       </c>
       <c r="R3" t="n">
-        <v>6380423</v>
+        <v>6380261</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124262395</v>
+        <v>124261792</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580974</v>
+        <v>581053</v>
       </c>
       <c r="R2" t="n">
-        <v>6380423</v>
+        <v>6380261</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124261792</v>
+        <v>124263681</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581053</v>
+        <v>581062</v>
       </c>
       <c r="R3" t="n">
-        <v>6380261</v>
+        <v>6380241</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124263681</v>
+        <v>124262395</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581062</v>
+        <v>580974</v>
       </c>
       <c r="R4" t="n">
-        <v>6380241</v>
+        <v>6380423</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124261792</v>
+        <v>124263147</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Östrahult, Östrahult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581053</v>
+        <v>580916</v>
       </c>
       <c r="R2" t="n">
-        <v>6380261</v>
+        <v>6380395</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124263147</v>
+        <v>124261792</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>95705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östrahult, Östrahult, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580916</v>
+        <v>581053</v>
       </c>
       <c r="R5" t="n">
-        <v>6380395</v>
+        <v>6380261</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17951-2025 artfynd.xlsx
+++ b/artfynd/A 17951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124263147</v>
+        <v>124262395</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östrahult, Östrahult, Sm</t>
+          <t>Rovkärret, Rovkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580916</v>
+        <v>580974</v>
       </c>
       <c r="R2" t="n">
-        <v>6380395</v>
+        <v>6380423</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124262395</v>
+        <v>124261792</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rovkärret, Rovkärret, Sm</t>
+          <t>Björkmossen, Björkmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580974</v>
+        <v>581053</v>
       </c>
       <c r="R4" t="n">
-        <v>6380423</v>
+        <v>6380261</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124261792</v>
+        <v>124263147</v>
       </c>
       <c r="B5" t="n">
-        <v>95705</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkmossen, Björkmossen, Sm</t>
+          <t>Östrahult, Östrahult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581053</v>
+        <v>580916</v>
       </c>
       <c r="R5" t="n">
-        <v>6380261</v>
+        <v>6380395</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
